--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/INDIANA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/INDIANA_2016.xlsx
@@ -2893,7 +2893,7 @@
         <v>117</v>
       </c>
       <c r="D141">
-        <v>0.009370494954348871</v>
+        <v>0.009370494954348873</v>
       </c>
     </row>
     <row r="142">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C274">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C661">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C737">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C757">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1109">
